--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:51</t>
+    <t xml:space="preserve">2026-09-10 01:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:01</t>
+    <t xml:space="preserve">2026-09-18 11:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:08</t>
+    <t xml:space="preserve">2026-09-23 14:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:31</t>
+    <t xml:space="preserve">2026-10-02 15:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:51</t>
+    <t xml:space="preserve">2026-10-04 10:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2019_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2019_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:18</t>
+    <t xml:space="preserve">2026-10-05 15:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
